--- a/target/test-classes/testdata.xlsx
+++ b/target/test-classes/testdata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{41874A1B-7B31-4D8C-B4BC-6254B62DFD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1CD144E2-8C76-4AB8-B742-298E2099B7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC0E13B9-8BBE-411E-A9EA-03EC6F57B0FE}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>username</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Doe</t>
-  </si>
-  <si>
-    <t>invalid</t>
   </si>
 </sst>
 </file>
@@ -483,14 +480,7 @@
         <v>400001</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/target/test-classes/testdata.xlsx
+++ b/target/test-classes/testdata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1CD144E2-8C76-4AB8-B742-298E2099B7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{6BFAB3AB-86DF-4756-B4D4-0A6916435A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC0E13B9-8BBE-411E-A9EA-03EC6F57B0FE}"/>
   </bookViews>
